--- a/Insurance Rate Data Scraper/output/or_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/or_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q48"/>
+  <dimension ref="A1:Q49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2801,12 +2801,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10/17/2025</t>
+          <t>09/19/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Artisan and Truckers Casualty Company</t>
+          <t>MGA Insurance Company, Inc.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2821,35 +2821,35 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-0.700%</t>
+          <t>6.300%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-0.200%</t>
+          <t>-3.000%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-422660</t>
+          <t>-180661</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>159623</v>
+        <v>2015</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>215211751</t>
+          <t>6465272</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>55.300%</t>
+          <t>10.000%</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-38.500%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>PRGS-134641954</t>
+          <t>GNSC-134675106</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2869,12 +2869,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134641954/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134675106/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Progressive Universal Insurance Company</t>
+          <t>Artisan and Truckers Casualty Company</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2906,35 +2906,35 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.400%</t>
+          <t>-0.700%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-0.100%</t>
+          <t>-0.200%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-320086</t>
+          <t>-422660</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>275869</v>
+        <v>159623</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>251667134</t>
+          <t>215211751</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>65.600%</t>
+          <t>55.300%</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-38.800%</t>
+          <t>-38.500%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01/16/2026</t>
+          <t>10/17/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Artisan and Truckers Casualty Company</t>
+          <t>Progressive Universal Insurance Company</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2991,35 +2991,35 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-3.700%</t>
+          <t>0.400%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>-0.100%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-4689412</t>
+          <t>-320086</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>155154</v>
+        <v>275869</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>214285533</t>
+          <t>251667134</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>3.600%</t>
+          <t>65.600%</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-8.100%</t>
+          <t>-38.800%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>PRGS-134771017</t>
+          <t>PRGS-134641954</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134771017/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134641954/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Progressive Universal Insurance Company</t>
+          <t>Artisan and Truckers Casualty Company</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3076,35 +3076,35 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-3.600%</t>
+          <t>-3.700%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-2.000%</t>
+          <t>-2.200%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-5321685</t>
+          <t>-4689412</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>283800</v>
+        <v>155154</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>261466362</t>
+          <t>214285533</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>3.500%</t>
+          <t>3.600%</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-12.500%</t>
+          <t>-8.100%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>06/21/2025</t>
+          <t>01/16/2026</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Oregon</t>
+          <t>Progressive Universal Insurance Company</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3156,40 +3156,40 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>12.300%</t>
+          <t>-3.600%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>12.300%</t>
+          <t>-2.000%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>411333</t>
+          <t>-5321685</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7299</v>
+        <v>283800</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3354748</t>
+          <t>261466362</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>30.400%</t>
+          <t>3.500%</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-12.500%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>LBPM-134491645</t>
+          <t>PRGS-134771017</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3207,9 +3207,14 @@
           <t>Filed</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134491645/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134771017/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3226,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>08/31/2025</t>
+          <t>06/21/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3236,40 +3241,40 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-8.500%</t>
+          <t>12.300%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-2.000%</t>
+          <t>12.300%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-3496174</t>
+          <t>411333</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>64985</v>
+        <v>7299</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>177643962</t>
+          <t>3354748</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>17.200%</t>
+          <t>30.400%</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-15.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3279,7 +3284,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>LBPM-134586842</t>
+          <t>LBPM-134491645</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3289,7 +3294,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134586842/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134491645/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3301,12 +3306,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>07/20/2025</t>
+          <t>08/31/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Safeco Insurance Company of Oregon</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3326,30 +3331,30 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-4.000%</t>
+          <t>-2.000%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-1100365</t>
+          <t>-3496174</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>12059</v>
+        <v>64985</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>27813955</t>
+          <t>177643962</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>118.500%</t>
+          <t>17.200%</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-62.800%</t>
+          <t>-15.100%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3359,7 +3364,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>LBPM-134586929</t>
+          <t>LBPM-134586842</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3369,7 +3374,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134586929/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134586842/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3386,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01/19/2026</t>
+          <t>07/20/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3401,35 +3406,35 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-8.500%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-4.000%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1100365</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>20837</v>
+        <v>12059</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>44213576</t>
+          <t>27813955</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>118.500%</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-62.800%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3439,7 +3444,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>LBPM-134733690</t>
+          <t>LBPM-134586929</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3449,7 +3454,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134733690/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134586929/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3466,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>01/19/2026</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3481,35 +3486,35 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-5.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-3.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-1300823</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>19230</v>
+        <v>20837</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>43394746</t>
+          <t>44213576</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>9.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-17.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3519,7 +3524,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>LBPM-134745304</t>
+          <t>LBPM-134733690</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3529,7 +3534,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134745304/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134733690/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3546,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3551,45 +3556,45 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.100%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-0.900%</t>
+          <t>-3.000%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-1053929</t>
+          <t>-1300823</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>63473</v>
+        <v>19230</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>113367175</t>
+          <t>43394746</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.500%</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-14.400%</t>
+          <t>-17.900%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3599,7 +3604,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>LBPM-134759261</t>
+          <t>LBPM-134745304</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3607,14 +3612,9 @@
           <t>Filed</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134759261/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134745304/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>03/15/2026</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3646,35 +3646,35 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>3.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2.410%</t>
+          <t>-0.900%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2403141</t>
+          <t>-1053929</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>58588</v>
+        <v>63473</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>99631185</t>
+          <t>113367175</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>3.320%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.210%</t>
+          <t>-14.400%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>LBPM-134826073</t>
+          <t>LBPM-134759261</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3694,12 +3694,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134826073/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134759261/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3711,55 +3711,55 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>03/15/2026</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.500%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.410%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2403141</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>31655</v>
+        <v>58588</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>56568405</t>
+          <t>99631185</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>25.000%</t>
+          <t>3.320%</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-24.600%</t>
+          <t>0.210%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>SFMA-134294129</t>
+          <t>LBPM-134826073</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134294129/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134826073/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3830,21 +3830,21 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>875163</v>
+        <v>31655</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>863774489</t>
+          <t>56568405</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>60.300%</t>
+          <t>25.000%</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-37.600%</t>
+          <t>-24.600%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3886,50 +3886,50 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>04.0002 Mobile Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>33.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>32.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3828378</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>15835</v>
+        <v>875163</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>11854928</t>
+          <t>863774489</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>59.600%</t>
+          <t>60.300%</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-19.300%</t>
+          <t>-37.600%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>SFMA-134421427</t>
+          <t>SFMA-134294129</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134421427/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134294129/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>04/15/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3976,25 +3976,45 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0002 Mobile Homeowners</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>33.000%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>32.300%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>3828378</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>36387</v>
+        <v>15835</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>63743659</t>
+          <t>11854928</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>59.600%</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>-19.300%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4004,7 +4024,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>SFMA-134491344</t>
+          <t>SFMA-134421427</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4014,12 +4034,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134491344/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134421427/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4036,7 +4056,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4055,11 +4075,11 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>962297</v>
+        <v>36387</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>891631927</t>
+          <t>63743659</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4096,12 +4116,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4116,20 +4136,15 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-3.600%</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>-2048236</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>33690</v>
+        <v>962297</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>56980415</t>
+          <t>891631927</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4139,7 +4154,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>SFMA-134619497</t>
+          <t>SFMA-134491344</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4149,12 +4164,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134619497/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134491344/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4186,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4186,20 +4201,20 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-4.200%</t>
+          <t>-3.600%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-38201187</t>
+          <t>-2048236</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>985050</v>
+        <v>33690</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>919545597</t>
+          <t>56980415</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4236,12 +4251,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12/15/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4256,30 +4271,20 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-3.600%</t>
+          <t>-4.200%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-1839005</t>
+          <t>-38201187</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>31896</v>
+        <v>985050</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>50889068</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>7.700%</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>-6.800%</t>
+          <t>919545597</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4289,7 +4294,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>SFMA-134700697</t>
+          <t>SFMA-134619497</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4299,12 +4304,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134700697/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134619497/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4321,68 +4326,148 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-3.600%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-1839005</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>31896</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>50889068</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>7.700%</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>-6.800%</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>SFMA-134700697</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134700697/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>12/15/2025</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>19.0 Personal Auto</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>-3.600%</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>-32649804</t>
         </is>
       </c>
-      <c r="I48" t="n">
+      <c r="I49" t="n">
         <v>1007104</v>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>908221048</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>0.500%</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>-10.100%</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>rate_change</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t>SFMA-134700697</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>Filed</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>output/pdfs/OR/134700697/filing_summary.pdf</t>
         </is>

--- a/Insurance Rate Data Scraper/output/or_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/or_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q49"/>
+  <dimension ref="A1:Q48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2036,55 +2036,55 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>08/18/2025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Peerless Indemnity Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>5.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-6.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-219687</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3240</v>
+        <v>125</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3531721</t>
+          <t>336683</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-1.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-7.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>LBPM-134342854</t>
+          <t>LBPM-134578347</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134342854/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134578347/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2155,11 +2155,11 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>125</v>
+        <v>17836</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>336683</t>
+          <t>54179090</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>08/18/2025</t>
+          <t>12/25/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2226,35 +2226,35 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.600%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.000%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>928</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>17836</v>
+        <v>37</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>54179090</t>
+          <t>92829</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>18.000%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-25.000%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>LBPM-134578347</t>
+          <t>LBPM-134773946</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2274,12 +2274,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134578347/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134773946/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2321,25 +2321,25 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>485664</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>37</v>
+        <v>18960</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>92829</t>
+          <t>48566349</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>18.000%</t>
+          <t>47.000%</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-25.000%</t>
+          <t>-81.000%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12/25/2025</t>
+          <t>02/28/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Artisan and Truckers Casualty Company</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2396,35 +2396,35 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>4.600%</t>
+          <t>7.400%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.000%</t>
+          <t>5.700%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>485664</t>
+          <t>11725846</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>18960</v>
+        <v>154310</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>48566349</t>
+          <t>205505042</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>47.000%</t>
+          <t>136.300%</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-81.000%</t>
+          <t>-28.200%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>LBPM-134773946</t>
+          <t>PRGS-134398058</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134773946/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134398058/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Artisan and Truckers Casualty Company</t>
+          <t>Progressive Universal Insurance Company</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2481,35 +2481,35 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>7.400%</t>
+          <t>2.600%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>5.700%</t>
+          <t>1.300%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>11725846</t>
+          <t>3157780</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>154310</v>
+        <v>260080</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>205505042</t>
+          <t>237272763</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>136.300%</t>
+          <t>35.400%</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-28.200%</t>
+          <t>-28.900%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>02/28/2025</t>
+          <t>09/19/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Progressive Universal Insurance Company</t>
+          <t>Artisan and Truckers Casualty Company</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2561,40 +2561,40 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2.600%</t>
+          <t>3.900%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.300%</t>
+          <t>4.100%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3157780</t>
+          <t>271254</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>260080</v>
+        <v>5487</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>237272763</t>
+          <t>6615950</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>35.400%</t>
+          <t>23.800%</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-28.900%</t>
+          <t>-11.100%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>PRGS-134398058</t>
+          <t>PRGS-134578217</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134398058/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134578217/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Artisan and Truckers Casualty Company</t>
+          <t>Progressive Universal Insurance Company</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2656,30 +2656,30 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>4.100%</t>
+          <t>3.700%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>271254</t>
+          <t>372679</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5487</v>
+        <v>9055</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>6615950</t>
+          <t>10072399</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>23.800%</t>
+          <t>24.300%</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-11.100%</t>
+          <t>-7.700%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Progressive Universal Insurance Company</t>
+          <t>MGA Insurance Company, Inc.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2731,40 +2731,40 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>3.900%</t>
+          <t>6.300%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>3.700%</t>
+          <t>-3.000%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>372679</t>
+          <t>-180661</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>9055</v>
+        <v>2015</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>10072399</t>
+          <t>6465272</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>24.300%</t>
+          <t>10.000%</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-7.700%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>PRGS-134578217</t>
+          <t>GNSC-134675106</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2784,12 +2784,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134578217/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134675106/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2801,12 +2801,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>09/19/2025</t>
+          <t>10/17/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MGA Insurance Company, Inc.</t>
+          <t>Artisan and Truckers Casualty Company</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2821,35 +2821,35 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>6.300%</t>
+          <t>-0.700%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-3.000%</t>
+          <t>-0.200%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-180661</t>
+          <t>-422660</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2015</v>
+        <v>159623</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>6465272</t>
+          <t>215211751</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>10.000%</t>
+          <t>55.300%</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>-38.500%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>GNSC-134675106</t>
+          <t>PRGS-134641954</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2869,12 +2869,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134675106/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134641954/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Artisan and Truckers Casualty Company</t>
+          <t>Progressive Universal Insurance Company</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2906,35 +2906,35 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-0.700%</t>
+          <t>0.400%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-0.200%</t>
+          <t>-0.100%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-422660</t>
+          <t>-320086</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>159623</v>
+        <v>275869</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>215211751</t>
+          <t>251667134</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>55.300%</t>
+          <t>65.600%</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-38.500%</t>
+          <t>-38.800%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10/17/2025</t>
+          <t>01/16/2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Progressive Universal Insurance Company</t>
+          <t>Artisan and Truckers Casualty Company</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2991,35 +2991,35 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.400%</t>
+          <t>-3.700%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.100%</t>
+          <t>-2.200%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-320086</t>
+          <t>-4689412</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>275869</v>
+        <v>155154</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>251667134</t>
+          <t>214285533</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>65.600%</t>
+          <t>3.600%</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-38.800%</t>
+          <t>-8.100%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>PRGS-134641954</t>
+          <t>PRGS-134771017</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134641954/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134771017/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Artisan and Truckers Casualty Company</t>
+          <t>Progressive Universal Insurance Company</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3076,35 +3076,35 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-3.700%</t>
+          <t>-3.600%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>-2.000%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-4689412</t>
+          <t>-5321685</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>155154</v>
+        <v>283800</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>214285533</t>
+          <t>261466362</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>3.600%</t>
+          <t>3.500%</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-8.100%</t>
+          <t>-12.500%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01/16/2026</t>
+          <t>06/21/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Progressive Universal Insurance Company</t>
+          <t>Safeco Insurance Company of Oregon</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3156,40 +3156,40 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-3.600%</t>
+          <t>12.300%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-2.000%</t>
+          <t>12.300%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-5321685</t>
+          <t>411333</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>283800</v>
+        <v>7299</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>261466362</t>
+          <t>3354748</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>3.500%</t>
+          <t>30.400%</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-12.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>PRGS-134771017</t>
+          <t>LBPM-134491645</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3207,14 +3207,9 @@
           <t>Filed</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134771017/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134491645/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3221,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>06/21/2025</t>
+          <t>08/31/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3241,40 +3236,40 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>12.300%</t>
+          <t>-8.500%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>12.300%</t>
+          <t>-2.000%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>411333</t>
+          <t>-3496174</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>7299</v>
+        <v>64985</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>3354748</t>
+          <t>177643962</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>30.400%</t>
+          <t>17.200%</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-15.100%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3284,7 +3279,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>LBPM-134491645</t>
+          <t>LBPM-134586842</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3294,7 +3289,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134491645/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134586842/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3306,12 +3301,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>08/31/2025</t>
+          <t>07/20/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Oregon</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3331,30 +3326,30 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-2.000%</t>
+          <t>-4.000%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-3496174</t>
+          <t>-1100365</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>64985</v>
+        <v>12059</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>177643962</t>
+          <t>27813955</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>17.200%</t>
+          <t>118.500%</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-15.100%</t>
+          <t>-62.800%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3364,7 +3359,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>LBPM-134586842</t>
+          <t>LBPM-134586929</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3374,7 +3369,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134586842/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134586929/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3381,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>07/20/2025</t>
+          <t>01/19/2026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3406,35 +3401,35 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-8.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-4.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-1100365</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>12059</v>
+        <v>20837</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>27813955</t>
+          <t>44213576</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>118.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-62.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3444,7 +3439,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>LBPM-134586929</t>
+          <t>LBPM-134733690</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3454,7 +3449,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134586929/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134733690/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3461,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01/19/2026</t>
+          <t>12/18/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3486,35 +3481,35 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.100%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-3.000%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1300823</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>20837</v>
+        <v>19230</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>44213576</t>
+          <t>43394746</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.500%</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-17.900%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3524,7 +3519,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>LBPM-134733690</t>
+          <t>LBPM-134745304</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3534,7 +3529,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134733690/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134745304/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3541,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12/18/2025</t>
+          <t>12/11/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3556,45 +3551,45 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-5.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-3.000%</t>
+          <t>-0.900%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-1300823</t>
+          <t>-1053929</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>19230</v>
+        <v>63473</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>43394746</t>
+          <t>113367175</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>9.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-17.900%</t>
+          <t>-14.400%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3604,7 +3599,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>LBPM-134745304</t>
+          <t>LBPM-134759261</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3612,9 +3607,14 @@
           <t>Filed</t>
         </is>
       </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134745304/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134759261/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12/11/2025</t>
+          <t>03/15/2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3646,35 +3646,35 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.500%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-0.900%</t>
+          <t>2.410%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-1053929</t>
+          <t>2403141</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>63473</v>
+        <v>58588</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>113367175</t>
+          <t>99631185</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.320%</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-14.400%</t>
+          <t>0.210%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>LBPM-134759261</t>
+          <t>LBPM-134826073</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3694,12 +3694,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134759261/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134826073/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3711,55 +3711,55 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>03/15/2026</t>
+          <t>04/15/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>3.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2.410%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2403141</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>58588</v>
+        <v>31655</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>99631185</t>
+          <t>56568405</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>3.320%</t>
+          <t>25.000%</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.210%</t>
+          <t>-24.600%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>LBPM-134826073</t>
+          <t>SFMA-134294129</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134826073/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134294129/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3830,21 +3830,21 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>31655</v>
+        <v>875163</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>56568405</t>
+          <t>863774489</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>25.000%</t>
+          <t>60.300%</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-24.600%</t>
+          <t>-37.600%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3886,50 +3886,50 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0002 Mobile Homeowners</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>33.000%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>32.300%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3828378</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>875163</v>
+        <v>15835</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>863774489</t>
+          <t>11854928</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>60.300%</t>
+          <t>59.600%</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-37.600%</t>
+          <t>-19.300%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>SFMA-134294129</t>
+          <t>SFMA-134421427</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134294129/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134421427/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>06/01/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3976,45 +3976,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>04.0002 Mobile Homeowners</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>33.000%</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>32.300%</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>3828378</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>15835</v>
+        <v>36387</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>11854928</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>59.600%</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>-19.300%</t>
+          <t>63743659</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4024,7 +4004,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>SFMA-134421427</t>
+          <t>SFMA-134491344</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4034,12 +4014,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134421427/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134491344/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4036,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4075,11 +4055,11 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>36387</v>
+        <v>962297</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>63743659</t>
+          <t>891631927</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4116,12 +4096,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>06/01/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4136,15 +4116,20 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-3.600%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-2048236</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>962297</v>
+        <v>33690</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>891631927</t>
+          <t>56980415</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4154,7 +4139,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>SFMA-134491344</t>
+          <t>SFMA-134619497</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4164,12 +4149,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134491344/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134619497/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4171,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4201,20 +4186,20 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-3.600%</t>
+          <t>-4.200%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-2048236</t>
+          <t>-38201187</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>33690</v>
+        <v>985050</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>56980415</t>
+          <t>919545597</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4251,12 +4236,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>12/15/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4271,20 +4256,30 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-4.200%</t>
+          <t>-3.600%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-38201187</t>
+          <t>-1839005</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>985050</v>
+        <v>31896</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>919545597</t>
+          <t>50889068</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>7.700%</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>-6.800%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4294,7 +4289,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>SFMA-134619497</t>
+          <t>SFMA-134700697</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4304,12 +4299,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134619497/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134700697/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4321,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4346,25 +4341,25 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-1839005</t>
+          <t>-32649804</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>31896</v>
+        <v>1007104</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>50889068</t>
+          <t>908221048</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>7.700%</t>
+          <t>0.500%</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-6.800%</t>
+          <t>-10.100%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4388,86 +4383,6 @@
         </is>
       </c>
       <c r="Q48" t="inlineStr">
-        <is>
-          <t>output/pdfs/OR/134700697/filing_summary.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>OR</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>12/15/2025</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>19.0 Personal Auto</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>19.0000 Personal Auto Combinations</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>-3.600%</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>-32649804</t>
-        </is>
-      </c>
-      <c r="I49" t="n">
-        <v>1007104</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>908221048</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>0.500%</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>-10.100%</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>rate_change</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>SFMA-134700697</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Filed</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
         <is>
           <t>output/pdfs/OR/134700697/filing_summary.pdf</t>
         </is>

--- a/Insurance Rate Data Scraper/output/or_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/or_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R132"/>
+  <dimension ref="A1:T132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,16 @@
           <t>validation_tier</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>external_validation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -592,6 +602,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -682,6 +702,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -772,6 +802,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -862,6 +902,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -952,6 +1002,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1042,6 +1102,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1132,6 +1202,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1222,6 +1302,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1312,6 +1402,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1402,6 +1502,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1492,6 +1602,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1582,6 +1702,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1672,6 +1802,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1759,7 +1899,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1999,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1939,7 +2099,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2199,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2299,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2399,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2499,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2599,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2699,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2799,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2899,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2999,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2834,7 +3094,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2927,6 +3197,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3017,6 +3297,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3104,7 +3394,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3197,6 +3497,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3287,6 +3597,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3377,6 +3697,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3467,6 +3797,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3557,6 +3897,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3647,6 +3997,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3737,6 +4097,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3827,6 +4197,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3917,6 +4297,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4007,6 +4397,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4097,6 +4497,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4187,6 +4597,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4277,6 +4697,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4367,6 +4797,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4457,6 +4897,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4547,6 +4997,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4637,6 +5097,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4727,6 +5197,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4814,7 +5294,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4907,6 +5397,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4997,6 +5497,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5087,6 +5597,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5177,6 +5697,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5267,6 +5797,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5357,6 +5897,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5447,6 +5997,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5537,6 +6097,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5627,6 +6197,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5717,6 +6297,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5807,6 +6397,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5897,6 +6497,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5987,6 +6597,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6077,6 +6697,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6167,6 +6797,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6257,6 +6897,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6347,6 +6997,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6437,6 +7097,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6527,6 +7197,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6617,6 +7297,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6707,6 +7397,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6797,6 +7497,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6884,7 +7594,17 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6974,7 +7694,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7794,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7894,17 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7994,17 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7334,7 +8094,17 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7424,7 +8194,17 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7517,6 +8297,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7607,6 +8397,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7694,7 +8494,17 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7787,6 +8597,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7877,6 +8697,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7967,6 +8797,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8057,6 +8897,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8147,6 +8997,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -8234,7 +9094,17 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8324,7 +9194,17 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8414,7 +9294,17 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8504,7 +9394,17 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8594,7 +9494,17 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8684,7 +9594,17 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8774,7 +9694,17 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8864,7 +9794,17 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8957,6 +9897,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9047,6 +9997,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9137,6 +10097,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9227,6 +10197,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9317,6 +10297,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9407,6 +10397,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9497,6 +10497,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9587,6 +10597,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9677,6 +10697,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9759,7 +10789,17 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9844,7 +10884,17 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9929,7 +10979,17 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10014,7 +11074,17 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10099,7 +11169,17 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10189,7 +11269,17 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10279,7 +11369,17 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10372,6 +11472,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10462,6 +11572,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -10552,6 +11672,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -10642,6 +11772,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10732,6 +11872,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10807,6 +11957,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10882,6 +12042,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -10972,6 +12142,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -11059,7 +12239,17 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -11149,7 +12339,17 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -11239,7 +12439,17 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -11309,7 +12519,17 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -11379,7 +12599,17 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -11454,7 +12684,17 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -11529,7 +12769,17 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -11614,7 +12864,17 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -11699,7 +12959,17 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -11787,6 +13057,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -11872,6 +13152,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -11962,6 +13252,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -12052,6 +13352,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -12140,6 +13450,16 @@
       <c r="R132" t="inlineStr">
         <is>
           <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/or_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/or_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T132"/>
+  <dimension ref="A1:U132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +517,11 @@
           <t>external_validation</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>match_strength</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -609,9 +614,10 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -709,9 +715,10 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -809,9 +816,10 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -909,9 +917,10 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1009,9 +1018,10 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1109,9 +1119,10 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1209,9 +1220,10 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1309,9 +1321,10 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1409,9 +1422,10 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1509,9 +1523,10 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1609,9 +1624,10 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1709,9 +1725,10 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1809,9 +1826,10 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1909,9 +1927,10 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2009,9 +2028,10 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2099,7 +2119,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2109,7 +2129,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2224,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2209,7 +2234,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2329,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2309,7 +2339,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2434,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2409,7 +2444,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -2509,9 +2549,10 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2609,9 +2650,10 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2709,9 +2751,10 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2809,9 +2852,10 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2899,7 +2943,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2909,7 +2953,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -3009,9 +3058,10 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3104,9 +3154,10 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3204,9 +3255,10 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3304,9 +3356,10 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3394,7 +3447,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3404,7 +3457,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -3504,9 +3562,10 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3604,9 +3663,10 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3704,9 +3764,10 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3804,9 +3865,10 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3904,9 +3966,10 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4004,9 +4067,10 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4104,9 +4168,10 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4204,9 +4269,10 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4304,9 +4370,10 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4404,9 +4471,10 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4504,9 +4572,10 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4604,9 +4673,10 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4704,9 +4774,10 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4804,9 +4875,10 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4904,9 +4976,10 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5004,9 +5077,10 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5104,9 +5178,10 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5204,9 +5279,10 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5304,9 +5380,10 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5404,9 +5481,10 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5504,9 +5582,10 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5604,9 +5683,10 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5704,9 +5784,10 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5804,9 +5885,10 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5904,9 +5986,10 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6004,9 +6087,10 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6104,9 +6188,10 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6204,9 +6289,10 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6304,9 +6390,10 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6404,9 +6491,10 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6504,9 +6592,10 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6604,9 +6693,10 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6704,9 +6794,10 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6804,9 +6895,10 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6904,9 +6996,10 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7004,9 +7097,10 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7104,9 +7198,10 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7204,9 +7299,10 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7304,9 +7400,10 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7404,9 +7501,10 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7504,9 +7602,10 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7604,9 +7703,10 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7704,9 +7804,10 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7804,9 +7905,10 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7894,7 +7996,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -7904,7 +8006,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -7994,7 +8101,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8004,7 +8111,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -8094,7 +8206,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8104,7 +8216,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -8194,7 +8311,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8204,7 +8321,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -8304,9 +8426,10 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8404,9 +8527,10 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8504,9 +8628,10 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8604,9 +8729,10 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8704,9 +8830,10 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8804,9 +8931,10 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8904,9 +9032,10 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9004,9 +9133,10 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9104,9 +9234,10 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9204,9 +9335,10 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9294,7 +9426,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -9304,7 +9436,12 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -9394,7 +9531,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -9404,7 +9541,12 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -9494,7 +9636,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -9504,7 +9646,12 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -9594,7 +9741,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -9604,7 +9751,12 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9846,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -9704,7 +9856,12 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -9794,7 +9951,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -9804,7 +9961,12 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -9904,9 +10066,10 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -10004,9 +10167,10 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10104,9 +10268,10 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10204,9 +10369,10 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -10304,9 +10470,10 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -10404,9 +10571,10 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10504,9 +10672,10 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10604,9 +10773,10 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10704,9 +10874,10 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10789,7 +10960,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -10799,7 +10970,12 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -10884,7 +11060,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -10894,7 +11070,12 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -10979,7 +11160,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -10989,7 +11170,12 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -11074,7 +11260,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -11084,7 +11270,12 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11360,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -11179,7 +11370,12 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -11279,9 +11475,10 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11379,9 +11576,10 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11479,9 +11677,10 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11579,9 +11778,10 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11679,9 +11879,10 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11779,9 +11980,10 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -11879,9 +12081,10 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -11964,9 +12167,10 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -12049,9 +12253,10 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -12149,9 +12354,10 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -12239,7 +12445,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -12249,7 +12455,12 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12550,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -12349,7 +12560,12 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -12449,9 +12665,10 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -12519,7 +12736,7 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
@@ -12529,7 +12746,12 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12821,7 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
@@ -12609,7 +12831,12 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -12684,7 +12911,7 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -12694,7 +12921,12 @@
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -12769,7 +13001,7 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
@@ -12779,7 +13011,12 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -12864,7 +13101,7 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
@@ -12874,7 +13111,12 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -12959,7 +13201,7 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>pipeline_only</t>
+          <t>ambest_validated</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
@@ -12969,7 +13211,12 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>unvalidated</t>
+          <t>ambest_cross_checked</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>direct</t>
         </is>
       </c>
     </row>
@@ -13064,9 +13311,10 @@
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -13159,9 +13407,10 @@
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -13259,9 +13508,10 @@
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -13359,9 +13609,10 @@
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -13459,9 +13710,10 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Insurance Rate Data Scraper/output/or_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/or_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U142"/>
+  <dimension ref="A1:U173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14405,12 +14405,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>09/19/2025</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MGA Insurance Company, Inc.</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -14425,35 +14425,35 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>6.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>-3.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>-180661</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2015</v>
+        <v>27151</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>6465272</t>
+          <t>48524981</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>10.000%</t>
+          <t>21.620%</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>-17.260%</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -14463,22 +14463,12 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>GNSC-134675106</t>
-        </is>
-      </c>
-      <c r="O141" t="inlineStr">
-        <is>
-          <t>Filed</t>
-        </is>
-      </c>
-      <c r="P141" t="inlineStr">
-        <is>
-          <t>2025-09-18</t>
+          <t>SFMA-134876448</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>output/pdfs/OR/134675106/filing_summary.pdf</t>
+          <t>output/pdfs/OR/134876448/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
@@ -14506,98 +14496,3049 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
+          <t>10/02/2026</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>903102</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>916406581</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>18.450%</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>-17.440%</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>SFMA-134876448</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134876448/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>08/01/2026</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>47.100%</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>9.900%</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>30409436</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>278633</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>308532607</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>77.200%</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>SFMA-134964038</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Review pending</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134964038/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>05/14/2026</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>GEICO Advantage Insurance Company</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>32197</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>44727960</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>12.400%</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>-14.000%</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>GECC-134942768</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134942768/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>05/14/2026</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>GEICO Marine Insurance Company</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>6545</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>11107370</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>23.000%</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>-17.400%</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>GECC-134942768</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134942768/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>GEICO Advantage Insurance Company</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>40554</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>51632724</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>GECC-135012126</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/135012126/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>GEICO Marine Insurance Company</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>8201</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>13317397</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>GECC-135012126</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/135012126/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Artisan and Truckers Casualty Company</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-4.900%</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>-10006527</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>148589</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>202322089</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>12.700%</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>-19.700%</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>PRGS-134900881</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134900881/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Progressive Universal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>-4.100%</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-3.200%</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-8483160</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>286212</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>262947766</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>8.400%</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>-18.700%</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>PRGS-134900881</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134900881/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>05/28/2026</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-2.600%</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-336442</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>8235</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>12940079</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>-6.000%</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>ALSE-134961166</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134961166/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>09/15/2026</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>2509</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>8994</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>14534304</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>1.500%</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>-3.400%</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>ALSE-134947608</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134947608/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>15.600%</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>5.000%</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>4323478</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>35084</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>86469552</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>14.400%</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>-27.300%</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>ALSE-135036610</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/135036610/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>07/21/2026</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>88507</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>82996959</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>ALSE-134974545</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Review pending</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134974545/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Fire Insurance Company</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>4.600%</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>105698</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>860</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>3529717</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>4.300%</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>1.800%</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>LBPM-134945410</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Review pending</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134945410/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>The First Liberty Insurance Corporation</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>4.600%</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>3.100%</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>8</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>27559</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>3.700%</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>1.900%</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>LBPM-134945410</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Review pending</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134945410/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>4.600%</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>3.200%</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>8209</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>146</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>260359</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>4.000%</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>1.300%</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>LBPM-134945724</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Review pending</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134945724/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>06/15/2026</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>-6.900%</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-6.200%</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>-3115468</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>22808</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>50575267</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>5.000%</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>-14.000%</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>LBPM-134953691</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134953691/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>06/13/2026</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Oregon</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>6694</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>2949408</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>LBPM-134939814</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134939814/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Oregon</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>-6.900%</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-0.400%</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>-595512</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>53688</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>147201870</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>8.000%</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>-28.000%</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>LBPM-134982767</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134982767/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Liberty Insurance Corporation</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>4.600%</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>812940</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>11594</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>27278165</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>3.600%</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>1.000%</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>LBPM-134944875</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Review pending</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134944875/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>05/22/2026</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Farmers Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>-9.600%</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-5.500%</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>-404562</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>3619</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>7355673</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>14.500%</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>-33.000%</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>rate_change_withdrawn</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>FAIG-134931227</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Withdrawn by company</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134931227/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>06/22/2026</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Farmers Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>-9.300%</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>-5.500%</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>-404562</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>3619</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>7355673</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>14.500%</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>-33.000%</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>FAIG-134959263</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Review pending</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134959263/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Farmers Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>660</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>2000942</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>50.200%</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>-32.700%</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>FAIG-134904944</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Review pending</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134904944/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Farmers Direct Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>3808</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>10264159</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>60.400%</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>-0.500%</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>FAIG-134904944</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Review pending</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134904944/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Farmers Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>8</v>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>25748</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>7.900%</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>-8.300%</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>FAIG-134904944</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Review pending</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134904944/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>01/09/2027</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>American Family Insurance Company</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>-2.100%</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>0.900%</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>219344</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>13200</v>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>24119902</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>151.400%</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>-65.200%</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>AMFC-134984855</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>Review pending</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134984855/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>07/13/2026</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Farmers Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>-8.400%</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>-956</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>4</v>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>11384</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>8.900%</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>-42.900%</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>FAIG-135011081</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/135011081/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>12/26/2026</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Garrison Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>58913930</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>USAA-134994627</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/135000560/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>12/26/2026</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>USAA Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>89803442</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>USAA-134994627</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/135000560/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>12/26/2026</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>USAA General Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>69571373</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>USAA-134994627</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/135000560/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>12/26/2026</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>United Services Automobile Association</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>58801844</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>USAA-134994627</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/135000560/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>09/19/2025</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>MGA Insurance Company, Inc.</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>6.300%</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-3.000%</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>-180661</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>2015</v>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>6465272</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>10.000%</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>GNSC-134675106</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>output/pdfs/OR/134675106/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
           <t>11/18/2024</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="C173" t="inlineStr">
         <is>
           <t>MGA Insurance Company, Inc.</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D173" t="inlineStr">
         <is>
           <t>19.0 Personal Auto</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="E173" t="inlineStr">
         <is>
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="F173" t="inlineStr">
         <is>
           <t>11.800%</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="G173" t="inlineStr">
         <is>
           <t>-2.500%</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
+      <c r="H173" t="inlineStr">
         <is>
           <t>-52747</t>
         </is>
       </c>
-      <c r="I142" t="n">
+      <c r="I173" t="n">
         <v>2295</v>
       </c>
-      <c r="J142" t="inlineStr">
+      <c r="J173" t="inlineStr">
         <is>
           <t>5288424</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
+      <c r="K173" t="inlineStr">
         <is>
           <t>10.000%</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
+      <c r="L173" t="inlineStr">
         <is>
           <t>-5.000%</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr">
+      <c r="M173" t="inlineStr">
         <is>
           <t>rate_change</t>
         </is>
       </c>
-      <c r="N142" t="inlineStr">
+      <c r="N173" t="inlineStr">
         <is>
           <t>GNSC-134314140</t>
         </is>
       </c>
-      <c r="O142" t="inlineStr">
+      <c r="O173" t="inlineStr">
         <is>
           <t>Filed</t>
         </is>
       </c>
-      <c r="P142" t="inlineStr">
+      <c r="P173" t="inlineStr">
         <is>
           <t>2024-11-15</t>
         </is>
       </c>
-      <c r="Q142" t="inlineStr">
+      <c r="Q173" t="inlineStr">
         <is>
           <t>output/pdfs/OR/134314140/filing_summary.pdf</t>
         </is>
       </c>
-      <c r="R142" t="inlineStr">
+      <c r="R173" t="inlineStr">
         <is>
           <t>pipeline_only</t>
         </is>
       </c>
-      <c r="S142" t="inlineStr">
+      <c r="S173" t="inlineStr">
         <is>
           <t>extension</t>
         </is>
       </c>
-      <c r="T142" t="inlineStr">
+      <c r="T173" t="inlineStr">
         <is>
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr"/>
+      <c r="U173" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
